--- a/ACID_WASH/Acid Wash Calculation.xlsx
+++ b/ACID_WASH/Acid Wash Calculation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamxi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramda\Documents\Zeta_Edit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C066DDDB-0337-4BE5-9344-D2981A4FB155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA03FD8-5DFD-4A78-BC08-A4F59AF55F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="5" activeTab="7" xr2:uid="{B75F2702-8E23-4918-BE92-C9BD16742AF7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="8" xr2:uid="{B75F2702-8E23-4918-BE92-C9BD16742AF7}"/>
   </bookViews>
   <sheets>
     <sheet name="PRELIMINARY CALCULATION" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="MAINTENANCE CLEARANCE &amp; ACCESS" sheetId="6" r:id="rId6"/>
     <sheet name="P&amp;ID Register" sheetId="7" r:id="rId7"/>
     <sheet name="Prelim Master GA &amp; PID Drawing" sheetId="8" r:id="rId8"/>
+    <sheet name="spesifikasi Colom" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="853">
   <si>
     <t>BASIS DESIGN</t>
   </si>
@@ -99,9 +100,6 @@
     <t>Temperature</t>
   </si>
   <si>
-    <t>Ambient</t>
-  </si>
-  <si>
     <t>HOLD</t>
   </si>
   <si>
@@ -2527,6 +2525,87 @@
   </si>
   <si>
     <t>Evaluate</t>
+  </si>
+  <si>
+    <t>&lt;50 °C</t>
+  </si>
+  <si>
+    <t>3-5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bahan : HDPE </t>
+  </si>
+  <si>
+    <t>fungsi : menampung carbon dan larutan asam sebanyak 5000 L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parameter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spesifikasi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satuan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keterangan </t>
+  </si>
+  <si>
+    <t>Kondisi Operasi : Suhu &lt;50  °C  dengan Konsentrasi HCL 3%-5%</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Tipe Tangki</t>
+  </si>
+  <si>
+    <t>Nama Alat</t>
+  </si>
+  <si>
+    <t>Kode Alat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acid Wash tank </t>
+  </si>
+  <si>
+    <t xml:space="preserve">vertical cylindrical tank </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material </t>
+  </si>
+  <si>
+    <t>HDPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapasitas Tank </t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>m³</t>
+  </si>
+  <si>
+    <t>dome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conical Frustum </t>
+  </si>
+  <si>
+    <t>Bagian bawah Tangki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagian Tangki </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diameter Tangki </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tinggi Tangki </t>
+  </si>
+  <si>
+    <t>Tank Acid Wash</t>
   </si>
 </sst>
 </file>
@@ -2868,7 +2947,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -3080,25 +3159,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3122,13 +3192,22 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3206,9 +3285,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3226,6 +3302,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3247,6 +3326,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -15750,7 +15832,7 @@
                           <a:schemeClr val="tx1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -16511,7 +16593,7 @@
                                   <a:schemeClr val="tx1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -16524,7 +16606,7 @@
                                   <a:schemeClr val="tx1"/>
                                 </a:solidFill>
                                 <a:effectLst/>
-                                <a:latin typeface="+mn-lt"/>
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 <a:ea typeface="+mn-ea"/>
                                 <a:cs typeface="+mn-cs"/>
                               </a:rPr>
@@ -16540,7 +16622,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -16929,7 +17011,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -16942,7 +17024,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -16956,7 +17038,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -21660,7 +21742,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -21673,7 +21755,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -21704,7 +21786,7 @@
                           <a:schemeClr val="tx1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -21728,7 +21810,7 @@
                           <a:schemeClr val="tx1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -21742,7 +21824,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -21755,7 +21837,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -21786,7 +21868,7 @@
                           <a:schemeClr val="tx1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -21800,7 +21882,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -21813,7 +21895,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -21844,7 +21926,7 @@
                           <a:schemeClr val="tx1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -21858,7 +21940,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -21871,7 +21953,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -21902,7 +21984,7 @@
                           <a:schemeClr val="tx1"/>
                         </a:solidFill>
                         <a:effectLst/>
-                        <a:latin typeface="+mn-lt"/>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         <a:ea typeface="+mn-ea"/>
                         <a:cs typeface="+mn-cs"/>
                       </a:rPr>
@@ -21916,7 +21998,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -21929,7 +22011,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -23723,19 +23805,19 @@
         <v>3</v>
       </c>
       <c r="G4" s="96" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H4" s="97"/>
       <c r="J4" s="96" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K4" s="97"/>
       <c r="S4" s="89" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T4" s="90"/>
       <c r="W4" s="94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X4" s="95"/>
     </row>
@@ -23750,28 +23832,28 @@
         <v>6</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="S5" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T5" s="26" t="s">
         <v>3</v>
       </c>
       <c r="W5" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="X5" s="26" t="s">
         <v>92</v>
-      </c>
-      <c r="X5" s="26" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.3">
@@ -23785,28 +23867,28 @@
         <v>6</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="J6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="S6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="T6" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="T6" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="W6" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X6" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="X6" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.3">
@@ -23820,28 +23902,28 @@
         <v>6</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="T7" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="T7" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="W7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="X7" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="X7" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="8" spans="2:24" x14ac:dyDescent="0.3">
@@ -23855,28 +23937,28 @@
         <v>6</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="W8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="X8" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="X8" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="9" spans="2:24" x14ac:dyDescent="0.3">
@@ -23890,28 +23972,28 @@
         <v>6</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="X9" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="X9" s="4" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.3">
@@ -23925,28 +24007,28 @@
         <v>6</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="J10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="S10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="T10" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="W10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="X10" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="X10" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.3">
@@ -23954,146 +24036,146 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
+        <v>826</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>18</v>
-      </c>
       <c r="G11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="J11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="S11" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="W11" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="X11" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="X11" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="12" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>827</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W12" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="X12" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="X12" s="4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="13" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
         <v>21</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>23</v>
-      </c>
       <c r="G13" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" s="17">
         <v>0.4</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K13" s="18">
         <v>0.49199999999999999</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W13" s="3"/>
       <c r="X13" s="4"/>
     </row>
     <row r="14" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W14" s="5"/>
       <c r="X14" s="7"/>
     </row>
     <row r="15" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>25</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="19" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:31" ht="21" x14ac:dyDescent="0.4">
       <c r="B20" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G20" s="2"/>
       <c r="J20" s="98" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K20" s="99"/>
       <c r="L20" s="99"/>
@@ -24102,11 +24184,11 @@
     </row>
     <row r="21" spans="2:31" ht="21" x14ac:dyDescent="0.4">
       <c r="B21" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" s="4"/>
       <c r="J21" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N21" s="4"/>
     </row>
@@ -24142,10 +24224,10 @@
     </row>
     <row r="27" spans="2:31" ht="21" x14ac:dyDescent="0.4">
       <c r="B27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" t="s">
         <v>29</v>
-      </c>
-      <c r="C27" t="s">
-        <v>30</v>
       </c>
       <c r="G27" s="4"/>
       <c r="J27" s="3"/>
@@ -24158,7 +24240,7 @@
       <c r="X27" s="24"/>
       <c r="Y27" s="24"/>
       <c r="AB27" s="91" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AC27" s="92"/>
       <c r="AD27" s="92"/>
@@ -24166,14 +24248,14 @@
     </row>
     <row r="28" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s">
         <v>31</v>
-      </c>
-      <c r="C28" t="s">
-        <v>32</v>
       </c>
       <c r="G28" s="4"/>
       <c r="J28" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N28" s="4"/>
       <c r="S28" s="24"/>
@@ -24188,10 +24270,10 @@
     </row>
     <row r="29" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" t="s">
         <v>33</v>
-      </c>
-      <c r="C29" t="s">
-        <v>34</v>
       </c>
       <c r="G29" s="4"/>
       <c r="J29" s="3"/>
@@ -24208,10 +24290,10 @@
     </row>
     <row r="30" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" t="s">
         <v>35</v>
-      </c>
-      <c r="C30" t="s">
-        <v>36</v>
       </c>
       <c r="G30" s="4"/>
       <c r="J30" s="3"/>
@@ -24258,7 +24340,7 @@
     </row>
     <row r="33" spans="2:31" ht="18" x14ac:dyDescent="0.35">
       <c r="B33" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G33" s="4"/>
       <c r="J33" s="3"/>
@@ -24275,11 +24357,11 @@
     </row>
     <row r="34" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G34" s="4"/>
       <c r="J34" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N34" s="4"/>
       <c r="S34" s="24"/>
@@ -24341,7 +24423,7 @@
       <c r="B38" s="3"/>
       <c r="G38" s="4"/>
       <c r="J38" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N38" s="4"/>
       <c r="S38" s="24"/>
@@ -24431,7 +24513,7 @@
     </row>
     <row r="44" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G44" s="4"/>
       <c r="J44" s="3"/>
@@ -24450,7 +24532,7 @@
       <c r="B45" s="3"/>
       <c r="G45" s="4"/>
       <c r="J45" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N45" s="4"/>
       <c r="S45" s="24"/>
@@ -24546,7 +24628,7 @@
       <c r="F51" s="6"/>
       <c r="G51" s="7"/>
       <c r="J51" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N51" s="4"/>
       <c r="S51" s="24"/>
@@ -24584,16 +24666,16 @@
     </row>
     <row r="54" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C54" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D54" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D54" s="21" t="s">
+      <c r="E54" s="22" t="s">
         <v>63</v>
-      </c>
-      <c r="E54" s="22" t="s">
-        <v>64</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="2"/>
@@ -24607,13 +24689,13 @@
     </row>
     <row r="55" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E55" s="4">
         <v>1.258</v>
@@ -24636,20 +24718,20 @@
     </row>
     <row r="56" spans="2:31" ht="21" x14ac:dyDescent="0.4">
       <c r="B56" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E56" s="4">
         <v>1.1319999999999999</v>
       </c>
       <c r="G56" s="4"/>
       <c r="J56" s="86" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K56" s="87"/>
       <c r="L56" s="87"/>
@@ -24667,13 +24749,13 @@
     </row>
     <row r="57" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E57" s="7">
         <v>1.0289999999999999</v>
@@ -24876,15 +24958,15 @@
       <c r="E7" s="24"/>
       <c r="F7" s="24"/>
       <c r="L7" s="91" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M7" s="92"/>
       <c r="N7" s="92"/>
       <c r="O7" s="93"/>
-      <c r="Q7" s="115" t="s">
-        <v>109</v>
-      </c>
-      <c r="R7" s="116"/>
+      <c r="Q7" s="101" t="s">
+        <v>108</v>
+      </c>
+      <c r="R7" s="102"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="24"/>
@@ -24895,10 +24977,10 @@
       <c r="L8" s="3"/>
       <c r="O8" s="4"/>
       <c r="Q8" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="R8" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
@@ -24910,10 +24992,10 @@
       <c r="L9" s="3"/>
       <c r="O9" s="4"/>
       <c r="Q9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="R9" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
@@ -24925,10 +25007,10 @@
       <c r="L10" s="3"/>
       <c r="O10" s="4"/>
       <c r="Q10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="R10" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
@@ -24940,10 +25022,10 @@
       <c r="L11" s="3"/>
       <c r="O11" s="4"/>
       <c r="Q11" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -24955,10 +25037,10 @@
       <c r="L12" s="3"/>
       <c r="O12" s="4"/>
       <c r="Q12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="R12" s="7" t="s">
         <v>117</v>
-      </c>
-      <c r="R12" s="7" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
@@ -25146,16 +25228,16 @@
     </row>
     <row r="35" spans="3:35" x14ac:dyDescent="0.3">
       <c r="C35" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D35" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="27" t="s">
+      <c r="F35" s="28" t="s">
         <v>120</v>
-      </c>
-      <c r="F35" s="28" t="s">
-        <v>121</v>
       </c>
       <c r="J35" s="23"/>
       <c r="K35" s="1"/>
@@ -25172,30 +25254,30 @@
       <c r="V35" s="1"/>
       <c r="W35" s="2"/>
       <c r="Y35" s="3"/>
-      <c r="Z35" s="109" t="s">
-        <v>208</v>
-      </c>
-      <c r="AA35" s="110"/>
-      <c r="AB35" s="111"/>
-      <c r="AD35" s="109" t="s">
-        <v>210</v>
-      </c>
-      <c r="AE35" s="110"/>
-      <c r="AF35" s="111"/>
+      <c r="Z35" s="106" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA35" s="107"/>
+      <c r="AB35" s="108"/>
+      <c r="AD35" s="106" t="s">
+        <v>209</v>
+      </c>
+      <c r="AE35" s="107"/>
+      <c r="AF35" s="108"/>
       <c r="AI35" s="4"/>
     </row>
     <row r="36" spans="3:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C36" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" t="s">
         <v>122</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="E36" s="29" t="s">
-        <v>124</v>
-      </c>
       <c r="F36" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J36" s="3"/>
       <c r="W36" s="4"/>
@@ -25208,178 +25290,178 @@
     </row>
     <row r="37" spans="3:35" x14ac:dyDescent="0.3">
       <c r="C37" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" t="s">
         <v>125</v>
-      </c>
-      <c r="D37" t="s">
-        <v>126</v>
       </c>
       <c r="E37" s="29">
         <v>1.5</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J37" s="3"/>
       <c r="L37" s="32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M37" s="33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N37" s="33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O37" s="34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W37" s="4"/>
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
       <c r="AB37" s="4"/>
       <c r="AD37" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="AE37" s="40" t="s">
         <v>211</v>
       </c>
-      <c r="AE37" s="40" t="s">
+      <c r="AF37" s="12" t="s">
         <v>212</v>
-      </c>
-      <c r="AF37" s="12" t="s">
-        <v>213</v>
       </c>
       <c r="AI37" s="4"/>
     </row>
     <row r="38" spans="3:35" x14ac:dyDescent="0.3">
       <c r="C38" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" t="s">
         <v>128</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="E38" s="29" t="s">
+      <c r="F38" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="J38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O38" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="W38" s="4"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
       <c r="AB38" s="4"/>
       <c r="AD38" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="AE38" s="40" t="s">
         <v>214</v>
       </c>
-      <c r="AE38" s="40" t="s">
+      <c r="AF38" s="12" t="s">
         <v>215</v>
-      </c>
-      <c r="AF38" s="12" t="s">
-        <v>216</v>
       </c>
       <c r="AI38" s="4"/>
     </row>
     <row r="39" spans="3:35" x14ac:dyDescent="0.3">
       <c r="C39" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" t="s">
         <v>132</v>
-      </c>
-      <c r="D39" t="s">
-        <v>133</v>
       </c>
       <c r="E39" s="29">
         <v>0.03</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J39" s="3"/>
       <c r="L39" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="N39" t="s">
+        <v>170</v>
+      </c>
+      <c r="O39" s="12" t="s">
         <v>163</v>
-      </c>
-      <c r="N39" t="s">
-        <v>171</v>
-      </c>
-      <c r="O39" s="12" t="s">
-        <v>164</v>
       </c>
       <c r="W39" s="4"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AB39" s="4"/>
       <c r="AD39" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="AE39" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="AE39" s="40" t="s">
+      <c r="AF39" s="12" t="s">
         <v>218</v>
-      </c>
-      <c r="AF39" s="12" t="s">
-        <v>219</v>
       </c>
       <c r="AI39" s="4"/>
     </row>
     <row r="40" spans="3:35" x14ac:dyDescent="0.3">
       <c r="C40" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D40" t="s">
         <v>134</v>
-      </c>
-      <c r="D40" t="s">
-        <v>135</v>
       </c>
       <c r="E40" s="29">
         <v>4</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J40" s="3"/>
       <c r="L40" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O40" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W40" s="4"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AB40" s="4"/>
       <c r="AD40" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="AE40" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="AE40" s="40" t="s">
+      <c r="AF40" s="12" t="s">
         <v>221</v>
-      </c>
-      <c r="AF40" s="12" t="s">
-        <v>222</v>
       </c>
       <c r="AI40" s="4"/>
     </row>
     <row r="41" spans="3:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C41" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D41" t="s">
         <v>136</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="E41" s="29" t="s">
+      <c r="F41" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>139</v>
       </c>
       <c r="J41" s="3"/>
       <c r="L41" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O41" s="12" t="s">
         <v>6</v>
@@ -25387,42 +25469,42 @@
       <c r="W41" s="4"/>
       <c r="Y41" s="3"/>
       <c r="Z41" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB41" s="4"/>
       <c r="AD41" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="AE41" s="42" t="s">
         <v>223</v>
       </c>
-      <c r="AE41" s="42" t="s">
+      <c r="AF41" s="13" t="s">
         <v>224</v>
-      </c>
-      <c r="AF41" s="13" t="s">
-        <v>225</v>
       </c>
       <c r="AI41" s="4"/>
     </row>
     <row r="42" spans="3:35" x14ac:dyDescent="0.3">
       <c r="C42" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D42" t="s">
         <v>140</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="E42" s="29" t="s">
-        <v>142</v>
-      </c>
       <c r="F42" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J42" s="3"/>
       <c r="L42" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O42" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="W42" s="4"/>
       <c r="Y42" s="3"/>
@@ -25432,25 +25514,25 @@
     </row>
     <row r="43" spans="3:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C43" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="E43" s="30"/>
       <c r="F43" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J43" s="3"/>
       <c r="L43" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M43" s="6"/>
       <c r="N43" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O43" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W43" s="4"/>
       <c r="Y43" s="3"/>
@@ -25475,41 +25557,41 @@
     </row>
     <row r="46" spans="3:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J46" s="3"/>
-      <c r="L46" s="107" t="s">
-        <v>174</v>
-      </c>
-      <c r="M46" s="117"/>
-      <c r="N46" s="117"/>
-      <c r="O46" s="108"/>
+      <c r="L46" s="103" t="s">
+        <v>173</v>
+      </c>
+      <c r="M46" s="104"/>
+      <c r="N46" s="104"/>
+      <c r="O46" s="105"/>
       <c r="W46" s="4"/>
       <c r="Y46" s="3"/>
       <c r="AI46" s="4"/>
     </row>
     <row r="47" spans="3:35" ht="21" x14ac:dyDescent="0.4">
       <c r="C47" s="31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J47" s="3"/>
       <c r="L47" s="3"/>
       <c r="O47" s="4"/>
       <c r="W47" s="4"/>
       <c r="Y47" s="3"/>
-      <c r="Z47" s="109" t="s">
-        <v>226</v>
-      </c>
-      <c r="AA47" s="110"/>
-      <c r="AB47" s="111"/>
+      <c r="Z47" s="106" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA47" s="107"/>
+      <c r="AB47" s="108"/>
       <c r="AD47" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="AE47" s="44" t="s">
         <v>228</v>
       </c>
-      <c r="AE47" s="44" t="s">
+      <c r="AF47" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="AG47" s="45" t="s">
         <v>229</v>
-      </c>
-      <c r="AF47" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="AG47" s="45" t="s">
-        <v>230</v>
       </c>
       <c r="AI47" s="4"/>
     </row>
@@ -25522,25 +25604,25 @@
       <c r="Z48" s="3"/>
       <c r="AB48" s="4"/>
       <c r="AD48" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="AE48" t="s">
         <v>231</v>
       </c>
-      <c r="AE48" t="s">
+      <c r="AF48" t="s">
         <v>232</v>
       </c>
-      <c r="AF48" t="s">
+      <c r="AG48" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="AG48" s="4" t="s">
-        <v>234</v>
-      </c>
       <c r="AI48" s="4"/>
     </row>
     <row r="49" spans="6:35" x14ac:dyDescent="0.3">
-      <c r="F49" s="107" t="s">
-        <v>145</v>
-      </c>
-      <c r="G49" s="117"/>
-      <c r="H49" s="108"/>
+      <c r="F49" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="G49" s="104"/>
+      <c r="H49" s="105"/>
       <c r="J49" s="3"/>
       <c r="L49" s="3"/>
       <c r="O49" s="4"/>
@@ -25549,28 +25631,28 @@
       <c r="Z49" s="3"/>
       <c r="AB49" s="4"/>
       <c r="AD49" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="AE49" t="s">
         <v>235</v>
       </c>
-      <c r="AE49" t="s">
+      <c r="AF49" t="s">
+        <v>232</v>
+      </c>
+      <c r="AG49" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="AF49" t="s">
-        <v>233</v>
-      </c>
-      <c r="AG49" s="4" t="s">
-        <v>237</v>
       </c>
       <c r="AI49" s="4"/>
     </row>
     <row r="50" spans="6:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F50" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="G50" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="G50" s="36" t="s">
+      <c r="H50" s="37" t="s">
         <v>147</v>
-      </c>
-      <c r="H50" s="37" t="s">
-        <v>148</v>
       </c>
       <c r="J50" s="3"/>
       <c r="L50" s="3"/>
@@ -25580,28 +25662,28 @@
       <c r="Z50" s="3"/>
       <c r="AB50" s="4"/>
       <c r="AD50" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="AE50" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AF50" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="AG50" s="7" t="s">
         <v>238</v>
-      </c>
-      <c r="AE50" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="AF50" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="AG50" s="7" t="s">
-        <v>239</v>
       </c>
       <c r="AI50" s="4"/>
     </row>
     <row r="51" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F51" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G51" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J51" s="3"/>
       <c r="L51" s="3"/>
@@ -25614,13 +25696,13 @@
     </row>
     <row r="52" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F52" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G52" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J52" s="3"/>
       <c r="L52" s="3"/>
@@ -25628,20 +25710,20 @@
       <c r="W52" s="4"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AB52" s="4"/>
       <c r="AI52" s="4"/>
     </row>
     <row r="53" spans="6:35" x14ac:dyDescent="0.3">
       <c r="F53" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G53" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J53" s="3"/>
       <c r="L53" s="3"/>
@@ -25654,13 +25736,13 @@
     </row>
     <row r="54" spans="6:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F54" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J54" s="3"/>
       <c r="L54" s="3"/>
@@ -25726,21 +25808,21 @@
     </row>
     <row r="61" spans="6:35" x14ac:dyDescent="0.3">
       <c r="J61" s="3"/>
-      <c r="L61" s="107" t="s">
-        <v>175</v>
-      </c>
-      <c r="M61" s="117"/>
-      <c r="N61" s="117"/>
-      <c r="O61" s="108"/>
-      <c r="Q61" s="107" t="s">
-        <v>181</v>
-      </c>
-      <c r="R61" s="117"/>
-      <c r="S61" s="108"/>
-      <c r="U61" s="107" t="s">
-        <v>186</v>
-      </c>
-      <c r="V61" s="108"/>
+      <c r="L61" s="103" t="s">
+        <v>174</v>
+      </c>
+      <c r="M61" s="104"/>
+      <c r="N61" s="104"/>
+      <c r="O61" s="105"/>
+      <c r="Q61" s="103" t="s">
+        <v>180</v>
+      </c>
+      <c r="R61" s="104"/>
+      <c r="S61" s="105"/>
+      <c r="U61" s="103" t="s">
+        <v>185</v>
+      </c>
+      <c r="V61" s="105"/>
       <c r="W61" s="4"/>
       <c r="Y61" s="3"/>
       <c r="AI61" s="4"/>
@@ -25760,18 +25842,18 @@
     <row r="63" spans="6:35" x14ac:dyDescent="0.3">
       <c r="J63" s="3"/>
       <c r="L63" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O63" s="4"/>
       <c r="Q63" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S63" s="4"/>
       <c r="U63" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V63" s="38" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="W63" s="4"/>
       <c r="Y63" s="3"/>
@@ -25784,10 +25866,10 @@
       <c r="Q64" s="3"/>
       <c r="S64" s="4"/>
       <c r="U64" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V64" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="W64" s="4"/>
       <c r="Y64" s="3"/>
@@ -25800,10 +25882,10 @@
       <c r="Q65" s="3"/>
       <c r="S65" s="4"/>
       <c r="U65" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="V65" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="W65" s="4"/>
       <c r="Y65" s="3"/>
@@ -25816,19 +25898,19 @@
       <c r="Q66" s="3"/>
       <c r="S66" s="4"/>
       <c r="U66" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="V66" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="W66" s="4"/>
       <c r="Y66" s="3"/>
-      <c r="Z66" s="112" t="s">
-        <v>240</v>
-      </c>
-      <c r="AA66" s="113"/>
-      <c r="AB66" s="113"/>
-      <c r="AC66" s="114"/>
+      <c r="Z66" s="109" t="s">
+        <v>239</v>
+      </c>
+      <c r="AA66" s="110"/>
+      <c r="AB66" s="110"/>
+      <c r="AC66" s="111"/>
       <c r="AI66" s="4"/>
     </row>
     <row r="67" spans="10:35" x14ac:dyDescent="0.3">
@@ -25838,10 +25920,10 @@
       <c r="Q67" s="3"/>
       <c r="S67" s="4"/>
       <c r="U67" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V67" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="W67" s="4"/>
       <c r="Y67" s="3"/>
@@ -25852,21 +25934,21 @@
     <row r="68" spans="10:35" x14ac:dyDescent="0.3">
       <c r="J68" s="3"/>
       <c r="L68" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O68" s="4"/>
       <c r="Q68" s="3"/>
       <c r="S68" s="4"/>
       <c r="U68" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="V68" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="W68" s="4"/>
       <c r="Y68" s="3"/>
       <c r="Z68" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AC68" s="4"/>
       <c r="AI68" s="4"/>
@@ -25878,10 +25960,10 @@
       <c r="Q69" s="3"/>
       <c r="S69" s="4"/>
       <c r="U69" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="V69" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="W69" s="4"/>
       <c r="Y69" s="3"/>
@@ -25896,10 +25978,10 @@
       <c r="Q70" s="3"/>
       <c r="S70" s="4"/>
       <c r="U70" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="V70" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="W70" s="4"/>
       <c r="Y70" s="3"/>
@@ -25912,14 +25994,14 @@
       <c r="L71" s="3"/>
       <c r="O71" s="4"/>
       <c r="Q71" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S71" s="4"/>
       <c r="U71" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="V71" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W71" s="4"/>
       <c r="Y71" s="3"/>
@@ -25934,10 +26016,10 @@
       <c r="Q72" s="3"/>
       <c r="S72" s="4"/>
       <c r="U72" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="V72" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W72" s="4"/>
       <c r="Y72" s="3"/>
@@ -25952,15 +26034,15 @@
       <c r="Q73" s="3"/>
       <c r="S73" s="4"/>
       <c r="U73" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="V73" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="W73" s="4"/>
       <c r="Y73" s="3"/>
       <c r="Z73" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AC73" s="4"/>
       <c r="AI73" s="4"/>
@@ -25972,10 +26054,10 @@
       <c r="Q74" s="3"/>
       <c r="S74" s="4"/>
       <c r="U74" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="V74" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W74" s="4"/>
       <c r="Y74" s="3"/>
@@ -25998,11 +26080,11 @@
     <row r="76" spans="10:35" x14ac:dyDescent="0.3">
       <c r="J76" s="3"/>
       <c r="L76" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O76" s="4"/>
       <c r="Q76" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S76" s="4"/>
       <c r="W76" s="4"/>
@@ -26063,14 +26145,14 @@
       <c r="S81" s="4"/>
       <c r="W81" s="4"/>
       <c r="Y81" s="3"/>
-      <c r="Z81" s="112" t="s">
+      <c r="Z81" s="109" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA81" s="110"/>
+      <c r="AB81" s="110" t="s">
         <v>243</v>
       </c>
-      <c r="AA81" s="113"/>
-      <c r="AB81" s="113" t="s">
-        <v>244</v>
-      </c>
-      <c r="AC81" s="114"/>
+      <c r="AC81" s="111"/>
       <c r="AI81" s="4"/>
     </row>
     <row r="82" spans="10:35" x14ac:dyDescent="0.3">
@@ -26081,14 +26163,14 @@
       <c r="S82" s="4"/>
       <c r="W82" s="4"/>
       <c r="Y82" s="3"/>
-      <c r="Z82" s="105" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA82" s="101"/>
-      <c r="AB82" s="101" t="s">
-        <v>246</v>
-      </c>
-      <c r="AC82" s="102"/>
+      <c r="Z82" s="112" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA82" s="113"/>
+      <c r="AB82" s="113" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC82" s="116"/>
       <c r="AI82" s="4"/>
     </row>
     <row r="83" spans="10:35" x14ac:dyDescent="0.3">
@@ -26099,34 +26181,34 @@
       <c r="S83" s="4"/>
       <c r="W83" s="4"/>
       <c r="Y83" s="3"/>
-      <c r="Z83" s="105" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA83" s="101"/>
-      <c r="AB83" s="101" t="s">
-        <v>247</v>
-      </c>
-      <c r="AC83" s="102"/>
+      <c r="Z83" s="112" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA83" s="113"/>
+      <c r="AB83" s="113" t="s">
+        <v>246</v>
+      </c>
+      <c r="AC83" s="116"/>
       <c r="AI83" s="4"/>
     </row>
     <row r="84" spans="10:35" x14ac:dyDescent="0.3">
       <c r="J84" s="3"/>
       <c r="L84" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O84" s="4"/>
       <c r="Q84" s="3"/>
       <c r="S84" s="4"/>
       <c r="W84" s="4"/>
       <c r="Y84" s="3"/>
-      <c r="Z84" s="105" t="s">
-        <v>151</v>
-      </c>
-      <c r="AA84" s="101"/>
-      <c r="AB84" s="101" t="s">
-        <v>248</v>
-      </c>
-      <c r="AC84" s="102"/>
+      <c r="Z84" s="112" t="s">
+        <v>150</v>
+      </c>
+      <c r="AA84" s="113"/>
+      <c r="AB84" s="113" t="s">
+        <v>247</v>
+      </c>
+      <c r="AC84" s="116"/>
       <c r="AI84" s="4"/>
     </row>
     <row r="85" spans="10:35" x14ac:dyDescent="0.3">
@@ -26137,14 +26219,14 @@
       <c r="S85" s="4"/>
       <c r="W85" s="4"/>
       <c r="Y85" s="3"/>
-      <c r="Z85" s="105" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA85" s="101"/>
-      <c r="AB85" s="101" t="s">
-        <v>249</v>
-      </c>
-      <c r="AC85" s="102"/>
+      <c r="Z85" s="112" t="s">
+        <v>151</v>
+      </c>
+      <c r="AA85" s="113"/>
+      <c r="AB85" s="113" t="s">
+        <v>248</v>
+      </c>
+      <c r="AC85" s="116"/>
       <c r="AI85" s="4"/>
     </row>
     <row r="86" spans="10:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -26152,19 +26234,19 @@
       <c r="L86" s="3"/>
       <c r="O86" s="4"/>
       <c r="Q86" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S86" s="4"/>
       <c r="W86" s="4"/>
       <c r="Y86" s="3"/>
-      <c r="Z86" s="106" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA86" s="103"/>
-      <c r="AB86" s="103" t="s">
-        <v>250</v>
-      </c>
-      <c r="AC86" s="104"/>
+      <c r="Z86" s="114" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA86" s="115"/>
+      <c r="AB86" s="115" t="s">
+        <v>249</v>
+      </c>
+      <c r="AC86" s="117"/>
       <c r="AI86" s="4"/>
     </row>
     <row r="87" spans="10:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -26205,7 +26287,7 @@
     <row r="90" spans="10:35" x14ac:dyDescent="0.3">
       <c r="J90" s="3"/>
       <c r="L90" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O90" s="4"/>
       <c r="Q90" s="3"/>
@@ -26275,12 +26357,16 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="L46:O46"/>
-    <mergeCell ref="L61:O61"/>
-    <mergeCell ref="Q61:S61"/>
+    <mergeCell ref="AB82:AC82"/>
+    <mergeCell ref="AB83:AC83"/>
+    <mergeCell ref="AB84:AC84"/>
+    <mergeCell ref="AB85:AC85"/>
+    <mergeCell ref="AB86:AC86"/>
+    <mergeCell ref="Z82:AA82"/>
+    <mergeCell ref="Z83:AA83"/>
+    <mergeCell ref="Z84:AA84"/>
+    <mergeCell ref="Z85:AA85"/>
+    <mergeCell ref="Z86:AA86"/>
     <mergeCell ref="U61:V61"/>
     <mergeCell ref="Z35:AB35"/>
     <mergeCell ref="AD35:AF35"/>
@@ -26288,16 +26374,12 @@
     <mergeCell ref="Z81:AA81"/>
     <mergeCell ref="AB81:AC81"/>
     <mergeCell ref="Z66:AC66"/>
-    <mergeCell ref="Z82:AA82"/>
-    <mergeCell ref="Z83:AA83"/>
-    <mergeCell ref="Z84:AA84"/>
-    <mergeCell ref="Z85:AA85"/>
-    <mergeCell ref="Z86:AA86"/>
-    <mergeCell ref="AB82:AC82"/>
-    <mergeCell ref="AB83:AC83"/>
-    <mergeCell ref="AB84:AC84"/>
-    <mergeCell ref="AB85:AC85"/>
-    <mergeCell ref="AB86:AC86"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="L46:O46"/>
+    <mergeCell ref="L61:O61"/>
+    <mergeCell ref="Q61:S61"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -26343,7 +26425,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -26361,7 +26443,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F5" s="4"/>
       <c r="L5" s="24"/>
@@ -26377,7 +26459,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F6" s="4"/>
       <c r="L6" s="24"/>
@@ -26393,7 +26475,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -26465,7 +26547,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="96" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H14" s="130"/>
       <c r="I14" s="97"/>
@@ -26479,13 +26561,13 @@
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
       <c r="G15" s="47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H15" s="48" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I15" s="49" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
@@ -26497,10 +26579,10 @@
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
       <c r="G16" s="46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>5</v>
@@ -26515,13 +26597,13 @@
     </row>
     <row r="17" spans="6:27" x14ac:dyDescent="0.3">
       <c r="G17" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H17" t="s">
+        <v>257</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>259</v>
       </c>
       <c r="L17" s="24"/>
       <c r="M17" s="24"/>
@@ -26533,13 +26615,13 @@
     </row>
     <row r="18" spans="6:27" x14ac:dyDescent="0.3">
       <c r="G18" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H18" t="s">
+        <v>256</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="H18" t="s">
-        <v>257</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>261</v>
       </c>
       <c r="L18" s="24"/>
       <c r="M18" s="24"/>
@@ -26551,79 +26633,79 @@
     </row>
     <row r="19" spans="6:27" x14ac:dyDescent="0.3">
       <c r="G19" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H19" t="s">
         <v>262</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="20" spans="6:27" x14ac:dyDescent="0.3">
       <c r="G20" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="H20" t="s">
         <v>265</v>
       </c>
-      <c r="H20" t="s">
-        <v>266</v>
-      </c>
       <c r="I20" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="6:27" x14ac:dyDescent="0.3">
       <c r="G21" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H21" t="s">
         <v>267</v>
       </c>
-      <c r="H21" t="s">
-        <v>268</v>
-      </c>
       <c r="I21" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="22" spans="6:27" x14ac:dyDescent="0.3">
       <c r="G22" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H22" t="s">
         <v>269</v>
       </c>
-      <c r="H22" t="s">
-        <v>270</v>
-      </c>
       <c r="I22" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="6:27" x14ac:dyDescent="0.3">
       <c r="G23" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="H23" t="s">
         <v>271</v>
       </c>
-      <c r="H23" t="s">
-        <v>272</v>
-      </c>
       <c r="I23" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="6:27" x14ac:dyDescent="0.3">
       <c r="G24" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="H24" t="s">
         <v>273</v>
       </c>
-      <c r="H24" t="s">
-        <v>274</v>
-      </c>
       <c r="I24" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" spans="6:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G25" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="I25" s="7" t="s">
         <v>280</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="26" spans="6:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -26639,24 +26721,24 @@
         <v>2</v>
       </c>
       <c r="G27" s="137" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H27" s="138"/>
       <c r="I27" s="139"/>
       <c r="L27" s="96" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M27" s="130"/>
       <c r="N27" s="130"/>
       <c r="O27" s="97"/>
       <c r="Q27" s="23" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="2"/>
       <c r="W27" s="118" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="X27" s="119"/>
       <c r="Y27" s="119"/>
@@ -26665,16 +26747,16 @@
     </row>
     <row r="28" spans="6:27" x14ac:dyDescent="0.3">
       <c r="G28" s="50" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H28" s="51" t="s">
+        <v>283</v>
+      </c>
+      <c r="I28" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="I28" s="52" t="s">
-        <v>285</v>
-      </c>
       <c r="L28" s="140" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M28" s="141"/>
       <c r="N28" s="141"/>
@@ -26683,22 +26765,22 @@
       <c r="Q28" s="3"/>
       <c r="T28" s="4"/>
       <c r="W28" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="X28" s="40" t="s">
         <v>304</v>
-      </c>
-      <c r="X28" s="40" t="s">
-        <v>305</v>
       </c>
       <c r="Y28">
         <v>1.5097700000000001</v>
       </c>
       <c r="Z28" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AA28" s="4"/>
     </row>
     <row r="29" spans="6:27" x14ac:dyDescent="0.3">
       <c r="G29" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -26711,13 +26793,13 @@
       <c r="Q29" s="3"/>
       <c r="T29" s="4"/>
       <c r="W29" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AA29" s="4"/>
     </row>
     <row r="30" spans="6:27" x14ac:dyDescent="0.3">
       <c r="G30" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H30">
         <v>1.2</v>
@@ -26730,23 +26812,23 @@
       <c r="Q30" s="3"/>
       <c r="T30" s="4"/>
       <c r="W30" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="X30" s="40" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Y30">
         <f>1.2 + 1.50977</f>
         <v>2.7097699999999998</v>
       </c>
       <c r="Z30" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AA30" s="4"/>
     </row>
     <row r="31" spans="6:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G31" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H31">
         <v>1.8</v>
@@ -26755,10 +26837,10 @@
         <v>1.8</v>
       </c>
       <c r="L31" s="39" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M31" s="40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O31" s="4"/>
       <c r="Q31" s="3"/>
@@ -26768,7 +26850,7 @@
     </row>
     <row r="32" spans="6:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G32" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H32" s="6">
         <v>4.407</v>
@@ -26791,7 +26873,7 @@
         <v>4</v>
       </c>
       <c r="W32" s="121" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="X32" s="122"/>
       <c r="Y32" s="122"/>
@@ -26800,28 +26882,28 @@
     </row>
     <row r="33" spans="7:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="Q33" s="54" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="R33" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="S33" s="55" t="s">
         <v>299</v>
       </c>
-      <c r="S33" s="55" t="s">
+      <c r="T33" s="56" t="s">
         <v>300</v>
-      </c>
-      <c r="T33" s="56" t="s">
-        <v>301</v>
       </c>
       <c r="W33" s="3"/>
       <c r="AA33" s="4"/>
     </row>
     <row r="34" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G34" s="131" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H34" s="132"/>
       <c r="I34" s="133"/>
       <c r="Q34" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="R34">
         <v>2.657</v>
@@ -26840,7 +26922,7 @@
       <c r="H35" s="135"/>
       <c r="I35" s="136"/>
       <c r="Q35" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R35">
         <v>2.157</v>
@@ -26852,10 +26934,10 @@
         <v>2.113</v>
       </c>
       <c r="W35" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="X35" s="40" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Y35">
         <f>4.15742-2.70977</f>
@@ -26865,7 +26947,7 @@
     </row>
     <row r="36" spans="7:27" x14ac:dyDescent="0.3">
       <c r="Q36" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="R36">
         <v>1.75</v>
@@ -26877,10 +26959,10 @@
         <v>1.706</v>
       </c>
       <c r="W36" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="X36" s="40" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Y36">
         <f>3.25 - 2.70977</f>
@@ -26890,7 +26972,7 @@
     </row>
     <row r="37" spans="7:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="Q37" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="R37" s="6">
         <v>1.25</v>
@@ -26910,32 +26992,32 @@
     <row r="41" spans="7:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="42" spans="7:27" x14ac:dyDescent="0.3">
       <c r="L42" s="124" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M42" s="125"/>
       <c r="N42" s="126"/>
     </row>
     <row r="43" spans="7:27" x14ac:dyDescent="0.3">
       <c r="L43" s="127" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M43" s="128"/>
       <c r="N43" s="129"/>
     </row>
     <row r="44" spans="7:27" x14ac:dyDescent="0.3">
       <c r="L44" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M44" s="57" t="s">
+        <v>317</v>
+      </c>
+      <c r="N44" s="26" t="s">
         <v>318</v>
-      </c>
-      <c r="N44" s="26" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="45" spans="7:27" x14ac:dyDescent="0.3">
       <c r="L45" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M45">
         <v>4.407</v>
@@ -26946,7 +27028,7 @@
     </row>
     <row r="46" spans="7:27" x14ac:dyDescent="0.3">
       <c r="L46" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M46">
         <v>4.157</v>
@@ -26957,7 +27039,7 @@
     </row>
     <row r="47" spans="7:27" x14ac:dyDescent="0.3">
       <c r="L47" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M47">
         <v>1.2</v>
@@ -26968,7 +27050,7 @@
     </row>
     <row r="48" spans="7:27" x14ac:dyDescent="0.3">
       <c r="L48" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M48">
         <v>1.448</v>
@@ -26979,7 +27061,7 @@
     </row>
     <row r="49" spans="12:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L49" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M49" s="6">
         <v>2.157</v>
@@ -27027,61 +27109,61 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="143" t="s">
-        <v>320</v>
-      </c>
-      <c r="E4" s="143"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="143"/>
+      <c r="D4" s="149" t="s">
+        <v>319</v>
+      </c>
+      <c r="E4" s="149"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
     </row>
     <row r="5" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C5">
         <v>2</v>
       </c>
-      <c r="D5" s="143" t="s">
-        <v>321</v>
-      </c>
-      <c r="E5" s="143"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
+      <c r="D5" s="149" t="s">
+        <v>320</v>
+      </c>
+      <c r="E5" s="149"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="149"/>
+      <c r="H5" s="149"/>
     </row>
     <row r="6" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C6">
         <v>3</v>
       </c>
-      <c r="D6" s="143" t="s">
-        <v>322</v>
-      </c>
-      <c r="E6" s="143"/>
-      <c r="F6" s="143"/>
-      <c r="G6" s="143"/>
-      <c r="H6" s="143"/>
+      <c r="D6" s="149" t="s">
+        <v>321</v>
+      </c>
+      <c r="E6" s="149"/>
+      <c r="F6" s="149"/>
+      <c r="G6" s="149"/>
+      <c r="H6" s="149"/>
     </row>
     <row r="7" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C7">
         <v>4</v>
       </c>
-      <c r="D7" s="143" t="s">
-        <v>323</v>
-      </c>
-      <c r="E7" s="143"/>
-      <c r="F7" s="143"/>
-      <c r="G7" s="143"/>
-      <c r="H7" s="143"/>
+      <c r="D7" s="149" t="s">
+        <v>322</v>
+      </c>
+      <c r="E7" s="149"/>
+      <c r="F7" s="149"/>
+      <c r="G7" s="149"/>
+      <c r="H7" s="149"/>
     </row>
     <row r="8" spans="3:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C8">
         <v>5</v>
       </c>
-      <c r="D8" s="143" t="s">
-        <v>324</v>
-      </c>
-      <c r="E8" s="143"/>
-      <c r="F8" s="143"/>
-      <c r="G8" s="143"/>
-      <c r="H8" s="143"/>
+      <c r="D8" s="149" t="s">
+        <v>323</v>
+      </c>
+      <c r="E8" s="149"/>
+      <c r="F8" s="149"/>
+      <c r="G8" s="149"/>
+      <c r="H8" s="149"/>
     </row>
     <row r="9" spans="3:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J9" s="68">
@@ -27093,31 +27175,31 @@
     </row>
     <row r="10" spans="3:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D10" s="23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="2"/>
-      <c r="J10" s="144" t="s">
-        <v>343</v>
-      </c>
-      <c r="K10" s="145"/>
-      <c r="L10" s="145"/>
-      <c r="M10" s="146"/>
-      <c r="O10" s="144" t="s">
-        <v>351</v>
-      </c>
-      <c r="P10" s="145"/>
-      <c r="Q10" s="145"/>
-      <c r="R10" s="146"/>
+      <c r="J10" s="143" t="s">
+        <v>342</v>
+      </c>
+      <c r="K10" s="144"/>
+      <c r="L10" s="144"/>
+      <c r="M10" s="145"/>
+      <c r="O10" s="143" t="s">
+        <v>350</v>
+      </c>
+      <c r="P10" s="144"/>
+      <c r="Q10" s="144"/>
+      <c r="R10" s="145"/>
       <c r="T10" s="69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U10" s="51" t="s">
+        <v>359</v>
+      </c>
+      <c r="V10" s="52" t="s">
         <v>360</v>
-      </c>
-      <c r="V10" s="52" t="s">
-        <v>361</v>
       </c>
       <c r="W10" s="61">
         <v>3</v>
@@ -27125,29 +27207,29 @@
     </row>
     <row r="11" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D11" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="J11" s="147" t="s">
-        <v>344</v>
-      </c>
-      <c r="K11" s="148"/>
-      <c r="L11" s="148"/>
-      <c r="M11" s="149"/>
+        <v>120</v>
+      </c>
+      <c r="J11" s="146" t="s">
+        <v>343</v>
+      </c>
+      <c r="K11" s="147"/>
+      <c r="L11" s="147"/>
+      <c r="M11" s="148"/>
       <c r="O11" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="R11" s="4"/>
       <c r="T11" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="U11" s="40">
         <v>5000</v>
@@ -27158,7 +27240,7 @@
     </row>
     <row r="12" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -27171,7 +27253,7 @@
       <c r="O12" s="3"/>
       <c r="R12" s="4"/>
       <c r="T12" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="U12" s="40">
         <v>4558</v>
@@ -27182,20 +27264,20 @@
     </row>
     <row r="13" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D13" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J13" s="3"/>
       <c r="M13" s="4"/>
       <c r="O13" s="3"/>
       <c r="R13" s="4"/>
       <c r="T13" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="U13" s="40">
         <v>1200</v>
@@ -27206,22 +27288,22 @@
     </row>
     <row r="14" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D14" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J14" s="3"/>
       <c r="M14" s="4"/>
       <c r="O14" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="R14" s="4"/>
       <c r="T14" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="U14" s="40">
         <v>3358</v>
@@ -27232,31 +27314,31 @@
     </row>
     <row r="15" spans="3:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D15" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K15" s="40" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L15" s="29">
         <f>1000/500</f>
         <v>2</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="O15" s="3"/>
       <c r="R15" s="4"/>
       <c r="T15" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="U15" s="42">
         <v>442</v>
@@ -27267,55 +27349,55 @@
     </row>
     <row r="16" spans="3:23" x14ac:dyDescent="0.3">
       <c r="D16" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="J16" s="147" t="s">
-        <v>347</v>
-      </c>
-      <c r="K16" s="148"/>
-      <c r="L16" s="148"/>
-      <c r="M16" s="149"/>
+        <v>340</v>
+      </c>
+      <c r="J16" s="146" t="s">
+        <v>346</v>
+      </c>
+      <c r="K16" s="147"/>
+      <c r="L16" s="147"/>
+      <c r="M16" s="148"/>
       <c r="O16" s="3"/>
       <c r="R16" s="4"/>
     </row>
     <row r="17" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D17" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J17" s="3"/>
       <c r="M17" s="4"/>
       <c r="O17" s="3"/>
       <c r="R17" s="4"/>
       <c r="T17" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="18" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D18" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F18" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J18" s="3"/>
       <c r="M18" s="4"/>
       <c r="O18" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P18">
         <f>(3.14*(1.5^2))/4</f>
@@ -27325,96 +27407,96 @@
     </row>
     <row r="19" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D19" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F19">
         <v>0.4</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K19" s="40" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L19" s="29">
         <f>0.4*2</f>
         <v>0.8</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P19" s="6">
         <f>P18*0.25</f>
         <v>0.44156250000000002</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="R19" s="7"/>
     </row>
     <row r="20" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D20" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F20" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="J20" s="147" t="s">
-        <v>349</v>
-      </c>
-      <c r="K20" s="148"/>
-      <c r="L20" s="148"/>
-      <c r="M20" s="149"/>
+        <v>341</v>
+      </c>
+      <c r="J20" s="146" t="s">
+        <v>348</v>
+      </c>
+      <c r="K20" s="147"/>
+      <c r="L20" s="147"/>
+      <c r="M20" s="148"/>
     </row>
     <row r="21" spans="4:21" x14ac:dyDescent="0.3">
       <c r="D21" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J21" s="3"/>
       <c r="M21" s="4"/>
     </row>
     <row r="22" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>138</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>139</v>
       </c>
       <c r="J22" s="3"/>
       <c r="M22" s="4"/>
     </row>
     <row r="23" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J23" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L23" s="30">
         <f>(1-0.4)*2</f>
         <v>1.2</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -27430,29 +27512,29 @@
       </c>
     </row>
     <row r="31" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D31" s="144" t="s">
-        <v>363</v>
-      </c>
-      <c r="E31" s="145"/>
-      <c r="F31" s="145"/>
-      <c r="G31" s="146"/>
-      <c r="I31" s="144" t="s">
-        <v>371</v>
-      </c>
-      <c r="J31" s="145"/>
-      <c r="K31" s="145"/>
-      <c r="L31" s="146"/>
-      <c r="N31" s="144" t="s">
-        <v>376</v>
-      </c>
-      <c r="O31" s="145"/>
-      <c r="P31" s="145"/>
-      <c r="Q31" s="146"/>
+      <c r="D31" s="143" t="s">
+        <v>362</v>
+      </c>
+      <c r="E31" s="144"/>
+      <c r="F31" s="144"/>
+      <c r="G31" s="145"/>
+      <c r="I31" s="143" t="s">
+        <v>370</v>
+      </c>
+      <c r="J31" s="144"/>
+      <c r="K31" s="144"/>
+      <c r="L31" s="145"/>
+      <c r="N31" s="143" t="s">
+        <v>375</v>
+      </c>
+      <c r="O31" s="144"/>
+      <c r="P31" s="144"/>
+      <c r="Q31" s="145"/>
       <c r="S31" s="50" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="T31" s="52" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U31" s="61">
         <v>7</v>
@@ -27462,103 +27544,103 @@
       <c r="D32" s="3"/>
       <c r="G32" s="4"/>
       <c r="I32" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J32" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K32">
         <v>1000</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N32" s="3"/>
       <c r="Q32" s="4"/>
       <c r="S32" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="T32" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="33" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D33" s="3"/>
       <c r="G33" s="4"/>
       <c r="I33" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L33" s="4"/>
       <c r="N33" s="3"/>
       <c r="Q33" s="4"/>
       <c r="S33" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="T33" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="34" spans="4:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D34" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E34" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I34" s="3"/>
       <c r="L34" s="4"/>
       <c r="N34" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O34" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P34">
         <f>5000-1200</f>
         <v>3800</v>
       </c>
       <c r="Q34" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="S34" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="35" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D35" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E35" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F35">
         <f>F34*U14</f>
         <v>3358</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J35" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K35">
         <f>(K32*9.81)/1000</f>
         <v>9.81</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N35" s="3"/>
       <c r="Q35" s="4"/>
@@ -27571,44 +27653,44 @@
       <c r="K36" s="6"/>
       <c r="L36" s="7"/>
       <c r="N36" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q36" s="4"/>
     </row>
     <row r="37" spans="4:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D37" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G37" s="4"/>
       <c r="N37" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O37" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P37">
         <f>1000+(1000*3.8)</f>
         <v>4800</v>
       </c>
       <c r="Q37" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="38" spans="4:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D38" s="3"/>
       <c r="G38" s="4"/>
       <c r="I38" s="65" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J38" s="66" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K38" s="66">
         <f>K35+F40</f>
         <v>42.751980000000003</v>
       </c>
       <c r="L38" s="67" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N38" s="3"/>
       <c r="Q38" s="4"/>
@@ -27617,50 +27699,50 @@
       <c r="D39" s="3"/>
       <c r="G39" s="4"/>
       <c r="N39" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q39" s="4"/>
     </row>
     <row r="40" spans="4:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D40" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F40" s="6">
         <f>(U14*9.81)/1000</f>
         <v>32.941980000000001</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P40" s="6">
         <f>(P37*9.81)/1000</f>
         <v>47.088000000000001</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="49" spans="3:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D49" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K50" s="143" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="K50" s="144" t="s">
-        <v>390</v>
-      </c>
-      <c r="L50" s="145"/>
-      <c r="M50" s="145"/>
-      <c r="N50" s="146"/>
+      <c r="L50" s="144"/>
+      <c r="M50" s="144"/>
+      <c r="N50" s="145"/>
     </row>
     <row r="51" spans="3:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" s="61">
@@ -27675,174 +27757,179 @@
     <row r="52" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K52" s="3"/>
       <c r="N52" s="4"/>
-      <c r="U52" s="144" t="s">
-        <v>394</v>
-      </c>
-      <c r="V52" s="145"/>
-      <c r="W52" s="145"/>
-      <c r="X52" s="146"/>
+      <c r="U52" s="143" t="s">
+        <v>393</v>
+      </c>
+      <c r="V52" s="144"/>
+      <c r="W52" s="144"/>
+      <c r="X52" s="145"/>
     </row>
     <row r="53" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K53" s="3"/>
       <c r="N53" s="4"/>
       <c r="U53" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="V53" t="s">
         <v>395</v>
       </c>
-      <c r="V53" t="s">
+      <c r="W53" t="s">
         <v>396</v>
       </c>
-      <c r="W53" t="s">
+      <c r="X53" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="X53" s="4" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="54" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K54" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="N54" s="4"/>
       <c r="U54" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="V54" t="s">
         <v>399</v>
       </c>
-      <c r="V54" t="s">
+      <c r="W54" t="s">
         <v>400</v>
       </c>
-      <c r="W54" t="s">
-        <v>401</v>
-      </c>
       <c r="X54" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="55" spans="3:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K55" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M55" s="6">
         <f>42.754/4</f>
         <v>10.688499999999999</v>
       </c>
       <c r="N55" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V55" t="s">
+        <v>401</v>
+      </c>
+      <c r="W55" t="s">
         <v>402</v>
       </c>
-      <c r="W55" t="s">
+      <c r="X55" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="X55" s="4" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="56" spans="3:24" x14ac:dyDescent="0.3">
       <c r="U56" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V56" t="s">
+        <v>405</v>
+      </c>
+      <c r="W56" t="s">
         <v>406</v>
       </c>
-      <c r="W56" t="s">
+      <c r="X56" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="X56" s="4" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="57" spans="3:24" x14ac:dyDescent="0.3">
       <c r="U57" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="V57" t="s">
         <v>409</v>
       </c>
-      <c r="V57" t="s">
-        <v>410</v>
-      </c>
       <c r="W57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="X57" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="3:24" x14ac:dyDescent="0.3">
       <c r="U58" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="V58" t="s">
         <v>411</v>
       </c>
-      <c r="V58" t="s">
+      <c r="W58" t="s">
         <v>412</v>
       </c>
-      <c r="W58" t="s">
-        <v>413</v>
-      </c>
       <c r="X58" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="3:24" x14ac:dyDescent="0.3">
       <c r="U59" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="V59" t="s">
         <v>414</v>
       </c>
-      <c r="V59" t="s">
-        <v>415</v>
-      </c>
       <c r="W59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="X59" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="60" spans="3:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="U60" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="V60" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="V60" s="6" t="s">
+      <c r="W60" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="W60" s="6" t="s">
+      <c r="X60" s="7" t="s">
         <v>418</v>
-      </c>
-      <c r="X60" s="7" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="63" spans="3:24" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="64" spans="3:24" x14ac:dyDescent="0.3">
       <c r="U64" s="80" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="V64" s="81"/>
       <c r="W64" s="82"/>
     </row>
     <row r="65" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U65" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V65" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="W65" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="66" spans="21:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="U66" s="5"/>
       <c r="V66" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="W66" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D8:H8"/>
     <mergeCell ref="K50:N50"/>
     <mergeCell ref="U52:X52"/>
     <mergeCell ref="U64:W64"/>
@@ -27854,11 +27941,6 @@
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="J11:M11"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D8:H8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -27882,316 +27964,316 @@
     <row r="5" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B6" s="150" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C6" s="151"/>
       <c r="D6" s="151"/>
       <c r="E6" s="152"/>
       <c r="G6" s="150" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H6" s="151"/>
       <c r="I6" s="151"/>
       <c r="J6" s="152"/>
       <c r="L6" s="150" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M6" s="151"/>
       <c r="N6" s="152"/>
-      <c r="P6" s="112" t="s">
-        <v>445</v>
-      </c>
-      <c r="Q6" s="113"/>
-      <c r="R6" s="113"/>
-      <c r="S6" s="114"/>
-      <c r="U6" s="112" t="s">
-        <v>460</v>
-      </c>
-      <c r="V6" s="113"/>
-      <c r="W6" s="114"/>
+      <c r="P6" s="109" t="s">
+        <v>444</v>
+      </c>
+      <c r="Q6" s="110"/>
+      <c r="R6" s="110"/>
+      <c r="S6" s="111"/>
+      <c r="U6" s="109" t="s">
+        <v>459</v>
+      </c>
+      <c r="V6" s="110"/>
+      <c r="W6" s="111"/>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E7" s="4"/>
       <c r="G7" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M7" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N7" s="4"/>
       <c r="P7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="R7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="S7" s="4"/>
       <c r="U7" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="V7">
         <v>2</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="40" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="4"/>
       <c r="G8" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I8">
         <v>1.2</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="M8" s="40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N8" s="4"/>
       <c r="P8" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q8">
         <v>1.5</v>
       </c>
       <c r="R8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S8" s="4"/>
       <c r="U8" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="V8">
         <v>1.7549999999999999</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D9" s="40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" s="4"/>
       <c r="G9" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I9">
         <v>0.6</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="M9" s="40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N9" s="4"/>
       <c r="P9" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S9" s="4"/>
       <c r="U9" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="V9">
         <v>2.7549999999999999</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" s="4"/>
       <c r="G10" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I10">
         <v>0.25</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N10" s="4"/>
       <c r="P10" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S10" s="4"/>
       <c r="U10" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="V10">
         <v>27.0123</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E11" s="4"/>
       <c r="G11" s="3"/>
       <c r="J11" s="4"/>
       <c r="L11" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M11" s="40">
         <v>0.03</v>
       </c>
       <c r="N11" s="4"/>
       <c r="P11" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S11" s="4"/>
       <c r="U11" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="V11" s="6">
         <v>0.54</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="12" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E12" s="4"/>
       <c r="G12" s="3"/>
       <c r="J12" s="4"/>
       <c r="L12" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="M12" s="40">
         <v>4</v>
       </c>
       <c r="N12" s="4"/>
       <c r="P12" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Q12">
         <v>1</v>
       </c>
       <c r="R12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S12" s="4"/>
     </row>
     <row r="13" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E13" s="4"/>
       <c r="G13" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I13" s="6">
         <f>I8+2.3</f>
         <v>3.5</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M13" s="40" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N13" s="4"/>
       <c r="P13" s="3"/>
@@ -28199,17 +28281,17 @@
     </row>
     <row r="14" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D14" s="40" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E14" s="4"/>
       <c r="L14" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M14" s="40" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N14" s="4"/>
       <c r="P14" s="3"/>
@@ -28217,7 +28299,7 @@
     </row>
     <row r="15" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D15" s="40">
         <v>0.4</v>
@@ -28230,110 +28312,110 @@
     </row>
     <row r="16" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E16" s="4"/>
       <c r="L16" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="N16" s="4"/>
       <c r="P16" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="R16">
         <v>1.5</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E17" s="4"/>
       <c r="L17" s="3"/>
       <c r="N17" s="4"/>
       <c r="P17" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q17" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="R17">
         <v>1</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E18" s="7"/>
       <c r="L18" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="N18" s="4"/>
       <c r="P18" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q18" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="R18">
         <f>R16+(2*R17)</f>
         <v>3.5</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="L19" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N19" s="4">
         <f>3.25-1.5</f>
         <v>1.75</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="R19">
         <f>R18*R18</f>
         <v>12.25</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="L20" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N20" s="4">
         <v>4.3959999999999999E-2</v>
@@ -28348,10 +28430,10 @@
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
       <c r="L21" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N21" s="4">
         <f>N19-N20</f>
@@ -28369,13 +28451,13 @@
       <c r="L22" s="3"/>
       <c r="N22" s="4"/>
       <c r="P22" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Q22">
         <v>1.5</v>
       </c>
       <c r="R22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="S22" s="4"/>
     </row>
@@ -28386,22 +28468,22 @@
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="L23" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M23">
         <v>1.75</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q23">
         <v>3.5</v>
       </c>
       <c r="R23" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="S23" s="4"/>
     </row>
@@ -28412,22 +28494,22 @@
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="L24" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M24">
         <v>1.25</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
       </c>
       <c r="R24" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="S24" s="4"/>
     </row>
@@ -28438,22 +28520,22 @@
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
       <c r="L25" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M25">
         <v>1.706</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q25">
         <v>12.25</v>
       </c>
       <c r="R25" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="S25" s="4"/>
     </row>
@@ -28464,13 +28546,13 @@
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
       <c r="L26" s="5" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M26" s="6">
         <v>1.206</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P26" s="5"/>
       <c r="Q26" s="6"/>
@@ -28560,7 +28642,7 @@
     <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="83" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C2" s="84"/>
       <c r="D2" s="84"/>
@@ -28569,29 +28651,29 @@
     </row>
     <row r="4" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B5" s="112" t="s">
+      <c r="B5" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="113"/>
-      <c r="D5" s="114"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="111"/>
       <c r="F5" s="73" t="s">
+        <v>477</v>
+      </c>
+      <c r="G5" s="74" t="s">
+        <v>395</v>
+      </c>
+      <c r="H5" s="110" t="s">
         <v>478</v>
       </c>
-      <c r="G5" s="74" t="s">
-        <v>396</v>
-      </c>
-      <c r="H5" s="113" t="s">
-        <v>479</v>
-      </c>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="114"/>
-      <c r="M5" s="144" t="s">
-        <v>493</v>
-      </c>
-      <c r="N5" s="145"/>
-      <c r="O5" s="145"/>
-      <c r="P5" s="146"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="111"/>
+      <c r="M5" s="143" t="s">
+        <v>492</v>
+      </c>
+      <c r="N5" s="144"/>
+      <c r="O5" s="144"/>
+      <c r="P5" s="145"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
@@ -28601,51 +28683,51 @@
         <v>2</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H6" s="155" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I6" s="155"/>
       <c r="J6" s="155"/>
       <c r="K6" s="156"/>
       <c r="M6" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O6" s="40">
         <v>1.8</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C7" s="40">
         <v>3.3959999999999999</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H7" s="155" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I7" s="155"/>
       <c r="J7" s="155"/>
@@ -28655,22 +28737,22 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C8" s="40">
         <v>1.5</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H8" s="155" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I8" s="155"/>
       <c r="J8" s="155"/>
@@ -28680,58 +28762,58 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C9" s="40">
         <v>2.2999999999999998</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H9" s="155" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I9" s="155"/>
       <c r="J9" s="155"/>
       <c r="K9" s="156"/>
       <c r="M9" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O9" s="40">
         <f>3.25-O6</f>
         <v>1.45</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C10" s="40">
         <v>0.6</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H10" s="153" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I10" s="153"/>
       <c r="J10" s="153"/>
@@ -28741,97 +28823,97 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C11" s="40">
         <v>0.15</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P11" s="4"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C12" s="40">
         <v>1000</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N12">
         <v>1.8</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P12" s="4"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C13" s="40">
         <v>1.2</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="N13">
         <v>3.25</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P13" s="4"/>
     </row>
     <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C14" s="40">
         <v>2.71</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="N14" s="6">
         <v>1.45</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P14" s="4"/>
     </row>
     <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C15" s="40">
         <v>3.25</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M15" s="5"/>
       <c r="N15" s="6"/>
@@ -28840,13 +28922,13 @@
     </row>
     <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C16" s="42">
         <v>3.5</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.3">
@@ -28879,7 +28961,7 @@
       <c r="C23" s="24"/>
       <c r="D23" s="24"/>
       <c r="M23" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
@@ -28959,13 +29041,13 @@
       <c r="L2" s="24"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="101" t="s">
-        <v>498</v>
-      </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="101"/>
+      <c r="B3" s="113" t="s">
+        <v>497</v>
+      </c>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
       <c r="G3" s="24"/>
       <c r="H3" s="24"/>
       <c r="I3" s="24"/>
@@ -28991,16 +29073,16 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
@@ -29011,13 +29093,13 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E7" s="4"/>
       <c r="G7" s="24"/>
@@ -29029,13 +29111,13 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E8" s="4"/>
       <c r="G8" s="24"/>
@@ -29047,13 +29129,13 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E9" s="4"/>
       <c r="G9" s="24"/>
@@ -29065,13 +29147,13 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C10" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D10" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E10" s="4"/>
       <c r="G10" s="24"/>
@@ -29083,13 +29165,13 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C11" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D11" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E11" s="4"/>
       <c r="G11" s="24"/>
@@ -29101,13 +29183,13 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E12" s="4"/>
       <c r="G12" s="24"/>
@@ -29119,13 +29201,13 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C13" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E13" s="4"/>
       <c r="G13" s="24"/>
@@ -29137,13 +29219,13 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C14" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D14" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E14" s="4"/>
       <c r="G14" s="24"/>
@@ -29155,13 +29237,13 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E15" s="4"/>
       <c r="G15" s="24"/>
@@ -29173,13 +29255,13 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C16" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D16" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E16" s="4"/>
       <c r="G16" s="24"/>
@@ -29191,13 +29273,13 @@
     </row>
     <row r="17" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="5" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E17" s="7"/>
       <c r="G17" s="24"/>
@@ -29225,7 +29307,7 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="80" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C20" s="81"/>
       <c r="D20" s="81"/>
@@ -29234,205 +29316,205 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C21" t="s">
         <v>529</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>530</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>531</v>
       </c>
-      <c r="E21" t="s">
-        <v>532</v>
-      </c>
       <c r="F21" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C22" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D22" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E22" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C23" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D23" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E23" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C24" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D24" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E24" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C25" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D25" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E25" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C26" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D26" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E26" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C27" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D27" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F27" s="4"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C28" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D28" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E28" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C29" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D29" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E29" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C30" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D30" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E30" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C31" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D31" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E31" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F31" s="4"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C32" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D32" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E32" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F32" s="4"/>
     </row>
     <row r="33" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F33" s="7"/>
     </row>
     <row r="34" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="80" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C35" s="81"/>
       <c r="D35" s="81"/>
@@ -29440,470 +29522,470 @@
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C36" t="s">
+        <v>570</v>
+      </c>
+      <c r="D36" t="s">
         <v>571</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" s="4" t="s">
         <v>572</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C37" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D37" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E37" s="4"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C38" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D38" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E38" s="4"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C39" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D39" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E39" s="4"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C40" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D40" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E40" s="4"/>
     </row>
     <row r="41" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B41" s="75" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C41" s="76" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D41" s="77" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E41" s="4"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C42" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D42" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E42" s="4"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C43" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D43" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C44" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D44" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E44" s="4"/>
     </row>
     <row r="45" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E45" s="7"/>
     </row>
     <row r="47" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="80" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C48" s="81"/>
       <c r="D48" s="82"/>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B49" s="39" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C49" s="40" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C50" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C51" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C52" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B53" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C53" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C54" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C55" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C56" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C57" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C58" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B59" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C59" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C60" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C61" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C62" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="63" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B63" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="65" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="66" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B66" s="80" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C66" s="81"/>
       <c r="D66" s="82"/>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C67" t="s">
         <v>644</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" s="4" t="s">
         <v>645</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C68" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B69" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C69" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B70" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C70" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B71" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C71" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C72" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B73" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C73" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C74" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C75" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B76" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C76" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B77" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C77" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B78" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C78" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B79" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C79" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B80" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C80" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="81" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B81" s="5" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>
@@ -29936,7 +30018,7 @@
     <row r="1" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G2" s="83" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H2" s="84"/>
       <c r="I2" s="84"/>
@@ -29945,21 +30027,21 @@
     </row>
     <row r="3" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="62" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D4" s="4"/>
       <c r="F4" s="24"/>
@@ -29971,7 +30053,7 @@
       <c r="L4" s="24"/>
       <c r="M4" s="24"/>
       <c r="O4" s="80" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="P4" s="81"/>
       <c r="Q4" s="81"/>
@@ -29980,10 +30062,10 @@
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C5" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D5" s="4"/>
       <c r="F5" s="24"/>
@@ -29995,25 +30077,25 @@
       <c r="L5" s="24"/>
       <c r="M5" s="24"/>
       <c r="O5" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="P5" t="s">
         <v>717</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>718</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>719</v>
-      </c>
-      <c r="R5" t="s">
-        <v>720</v>
       </c>
       <c r="S5" s="4"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D6" s="4"/>
       <c r="F6" s="24"/>
@@ -30025,25 +30107,25 @@
       <c r="L6" s="24"/>
       <c r="M6" s="24"/>
       <c r="O6" s="3" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="P6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="R6" s="40" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="S6" s="12"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C7" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D7" s="4"/>
       <c r="F7" s="24"/>
@@ -30055,25 +30137,25 @@
       <c r="L7" s="24"/>
       <c r="M7" s="24"/>
       <c r="O7" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="P7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="R7" s="71" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="S7" s="72"/>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D8" s="4"/>
       <c r="F8" s="24"/>
@@ -30085,25 +30167,25 @@
       <c r="L8" s="24"/>
       <c r="M8" s="24"/>
       <c r="O8" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="P8" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="Q8" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="R8" s="29" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="S8" s="78"/>
     </row>
     <row r="9" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C9" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D9" s="4"/>
       <c r="F9" s="24"/>
@@ -30115,25 +30197,25 @@
       <c r="L9" s="24"/>
       <c r="M9" s="24"/>
       <c r="O9" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="S9" s="79"/>
     </row>
     <row r="10" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D10" s="4"/>
       <c r="F10" s="24"/>
@@ -30147,10 +30229,10 @@
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C11" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D11" s="4"/>
       <c r="F11" s="24"/>
@@ -30162,7 +30244,7 @@
       <c r="L11" s="24"/>
       <c r="M11" s="24"/>
       <c r="O11" s="80" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="P11" s="81"/>
       <c r="Q11" s="81"/>
@@ -30171,10 +30253,10 @@
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C12" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D12" s="4"/>
       <c r="F12" s="24"/>
@@ -30186,25 +30268,25 @@
       <c r="L12" s="24"/>
       <c r="M12" s="24"/>
       <c r="O12" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="P12" t="s">
         <v>732</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>733</v>
       </c>
-      <c r="Q12" t="s">
-        <v>734</v>
-      </c>
       <c r="R12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="S12" s="4"/>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C13" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D13" s="4"/>
       <c r="F13" s="24"/>
@@ -30216,22 +30298,22 @@
       <c r="L13" s="24"/>
       <c r="M13" s="24"/>
       <c r="O13" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="P13" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="Q13" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="S13" s="4"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C14" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D14" s="4"/>
       <c r="F14" s="24"/>
@@ -30243,22 +30325,22 @@
       <c r="L14" s="24"/>
       <c r="M14" s="24"/>
       <c r="O14" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="P14" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="Q14" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="S14" s="4"/>
     </row>
     <row r="15" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D15" s="7"/>
       <c r="F15" s="24"/>
@@ -30270,13 +30352,13 @@
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
       <c r="O15" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="P15" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="Q15" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="S15" s="4"/>
     </row>
@@ -30290,13 +30372,13 @@
       <c r="L16" s="24"/>
       <c r="M16" s="24"/>
       <c r="O16" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="P16" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="Q16" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="S16" s="4"/>
     </row>
@@ -30310,13 +30392,13 @@
       <c r="L17" s="24"/>
       <c r="M17" s="24"/>
       <c r="O17" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="P17" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="Q17" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="S17" s="4"/>
     </row>
@@ -30330,13 +30412,13 @@
       <c r="L18" s="24"/>
       <c r="M18" s="24"/>
       <c r="O18" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="P18" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="Q18" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="S18" s="4"/>
     </row>
@@ -30350,13 +30432,13 @@
       <c r="L19" s="24"/>
       <c r="M19" s="24"/>
       <c r="O19" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="P19" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="Q19" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="S19" s="4"/>
     </row>
@@ -30370,37 +30452,37 @@
       <c r="L20" s="24"/>
       <c r="M20" s="24"/>
       <c r="O20" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="P20" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="Q20" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="S20" s="4"/>
     </row>
     <row r="21" spans="6:19" x14ac:dyDescent="0.3">
       <c r="O21" s="3" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="P21" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="Q21" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="S21" s="4"/>
     </row>
     <row r="22" spans="6:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="O22" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="R22" s="6"/>
       <c r="S22" s="7"/>
@@ -30425,7 +30507,7 @@
       <c r="L24" s="24"/>
       <c r="M24" s="24"/>
       <c r="O24" s="80" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="P24" s="81"/>
       <c r="Q24" s="81"/>
@@ -30442,16 +30524,16 @@
       <c r="L25" s="24"/>
       <c r="M25" s="24"/>
       <c r="O25" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="P25" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Q25" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="R25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="S25" s="4"/>
     </row>
@@ -30465,13 +30547,13 @@
       <c r="L26" s="24"/>
       <c r="M26" s="24"/>
       <c r="O26" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="P26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q26" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="S26" s="4"/>
     </row>
@@ -30485,13 +30567,13 @@
       <c r="L27" s="24"/>
       <c r="M27" s="24"/>
       <c r="O27" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q27" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="S27" s="4"/>
     </row>
@@ -30505,13 +30587,13 @@
       <c r="L28" s="24"/>
       <c r="M28" s="24"/>
       <c r="O28" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="P28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q28" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="S28" s="4"/>
     </row>
@@ -30525,13 +30607,13 @@
       <c r="L29" s="24"/>
       <c r="M29" s="24"/>
       <c r="O29" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q29" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="S29" s="4"/>
     </row>
@@ -30545,13 +30627,13 @@
       <c r="L30" s="24"/>
       <c r="M30" s="24"/>
       <c r="O30" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="P30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q30" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="S30" s="4"/>
     </row>
@@ -30565,13 +30647,13 @@
       <c r="L31" s="24"/>
       <c r="M31" s="24"/>
       <c r="O31" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="P31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q31" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="S31" s="4"/>
     </row>
@@ -30585,13 +30667,13 @@
       <c r="L32" s="24"/>
       <c r="M32" s="24"/>
       <c r="O32" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="P32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q32" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="S32" s="4"/>
     </row>
@@ -30605,13 +30687,13 @@
       <c r="L33" s="24"/>
       <c r="M33" s="24"/>
       <c r="O33" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="P33" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="Q33" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="S33" s="4"/>
     </row>
@@ -30625,13 +30707,13 @@
       <c r="L34" s="24"/>
       <c r="M34" s="24"/>
       <c r="O34" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="P34" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="Q34" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="S34" s="4"/>
     </row>
@@ -30645,13 +30727,13 @@
       <c r="L35" s="24"/>
       <c r="M35" s="24"/>
       <c r="O35" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="P35" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="Q35" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="S35" s="4"/>
     </row>
@@ -30665,13 +30747,13 @@
       <c r="L36" s="24"/>
       <c r="M36" s="24"/>
       <c r="O36" s="5" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="R36" s="6"/>
       <c r="S36" s="7"/>
@@ -30696,7 +30778,7 @@
       <c r="L38" s="24"/>
       <c r="M38" s="24"/>
       <c r="O38" s="80" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P38" s="81"/>
       <c r="Q38" s="81"/>
@@ -30705,16 +30787,16 @@
     </row>
     <row r="39" spans="6:19" x14ac:dyDescent="0.3">
       <c r="O39" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="P39" t="s">
+        <v>784</v>
+      </c>
+      <c r="Q39" t="s">
         <v>785</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="R39" t="s">
         <v>786</v>
-      </c>
-      <c r="R39" t="s">
-        <v>787</v>
       </c>
       <c r="S39" s="4"/>
     </row>
@@ -30728,16 +30810,16 @@
       <c r="L40" s="24"/>
       <c r="M40" s="24"/>
       <c r="O40" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="P40" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="Q40" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="R40" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="S40" s="4"/>
     </row>
@@ -30751,16 +30833,16 @@
       <c r="L41" s="24"/>
       <c r="M41" s="24"/>
       <c r="O41" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="P41" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="Q41" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="R41" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="S41" s="4"/>
     </row>
@@ -30774,16 +30856,16 @@
       <c r="L42" s="24"/>
       <c r="M42" s="24"/>
       <c r="O42" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="P42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q42" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="R42" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="S42" s="4"/>
     </row>
@@ -30797,16 +30879,16 @@
       <c r="L43" s="24"/>
       <c r="M43" s="24"/>
       <c r="O43" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="P43" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="Q43" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="R43" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="S43" s="4"/>
     </row>
@@ -30820,16 +30902,16 @@
       <c r="L44" s="24"/>
       <c r="M44" s="24"/>
       <c r="O44" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="P44" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="Q44" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="R44" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="S44" s="4"/>
     </row>
@@ -30843,16 +30925,16 @@
       <c r="L45" s="24"/>
       <c r="M45" s="24"/>
       <c r="O45" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="P45" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="Q45" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="R45" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="S45" s="4"/>
     </row>
@@ -30866,16 +30948,16 @@
       <c r="L46" s="24"/>
       <c r="M46" s="24"/>
       <c r="O46" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="P46" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="Q46" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="R46" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="S46" s="4"/>
     </row>
@@ -30889,16 +30971,16 @@
       <c r="L47" s="24"/>
       <c r="M47" s="24"/>
       <c r="O47" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="P47" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="Q47" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="R47" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="S47" s="4"/>
     </row>
@@ -30912,16 +30994,16 @@
       <c r="L48" s="24"/>
       <c r="M48" s="24"/>
       <c r="O48" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P48" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="Q48" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="R48" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="S48" s="4"/>
     </row>
@@ -30935,16 +31017,16 @@
       <c r="L49" s="24"/>
       <c r="M49" s="24"/>
       <c r="O49" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="P49" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="Q49" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R49" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="S49" s="4"/>
     </row>
@@ -30958,16 +31040,16 @@
       <c r="L50" s="24"/>
       <c r="M50" s="24"/>
       <c r="O50" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="P50" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="Q50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R50" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="S50" s="4"/>
     </row>
@@ -30981,16 +31063,16 @@
       <c r="L51" s="24"/>
       <c r="M51" s="24"/>
       <c r="O51" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="P51" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="Q51" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="R51" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="S51" s="4"/>
     </row>
@@ -31004,16 +31086,16 @@
       <c r="L52" s="24"/>
       <c r="M52" s="24"/>
       <c r="O52" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="P52" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="Q52" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="R52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S52" s="4"/>
     </row>
@@ -31027,16 +31109,16 @@
       <c r="L53" s="24"/>
       <c r="M53" s="24"/>
       <c r="O53" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="P53" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="Q53" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="R53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S53" s="4"/>
     </row>
@@ -31050,16 +31132,16 @@
       <c r="L54" s="24"/>
       <c r="M54" s="24"/>
       <c r="O54" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="P54" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="Q54" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="R54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S54" s="4"/>
     </row>
@@ -31073,14 +31155,14 @@
       <c r="L55" s="24"/>
       <c r="M55" s="24"/>
       <c r="O55" s="5" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="P55" s="6"/>
       <c r="Q55" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S55" s="7"/>
     </row>
@@ -31096,4 +31178,325 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CAB3E29-1D30-4C03-8312-AD4B8B950B43}">
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="157" t="s">
+        <v>852</v>
+      </c>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="113" t="s">
+        <v>829</v>
+      </c>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="149" t="s">
+        <v>828</v>
+      </c>
+      <c r="B4" s="149"/>
+      <c r="C4" s="149"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="149"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="113" t="s">
+        <v>834</v>
+      </c>
+      <c r="B5" s="113"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="40" t="s">
+        <v>835</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>830</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>831</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>832</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="40">
+        <v>1</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>837</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>839</v>
+      </c>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="40">
+        <v>2</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>838</v>
+      </c>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="40">
+        <v>3</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>836</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>840</v>
+      </c>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="40">
+        <v>4</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>841</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>842</v>
+      </c>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="40">
+        <v>5</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>843</v>
+      </c>
+      <c r="C12" s="40">
+        <v>5000</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="40"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="40">
+        <v>6</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>844</v>
+      </c>
+      <c r="C13" s="40">
+        <v>5</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>845</v>
+      </c>
+      <c r="E13" s="40"/>
+      <c r="J13" s="96" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" s="97"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="40">
+        <v>7</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>849</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>846</v>
+      </c>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="J14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="40">
+        <v>8</v>
+      </c>
+      <c r="B15" s="40" t="s">
+        <v>848</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>847</v>
+      </c>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="J15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="40">
+        <v>9</v>
+      </c>
+      <c r="B16" s="40" t="s">
+        <v>850</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="J16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="40">
+        <v>10</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>851</v>
+      </c>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="J17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="40">
+        <v>11</v>
+      </c>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="J18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="40"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="J19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="40"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="J20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="40"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="J21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="40"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="J22" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K22" s="18">
+        <v>0.49199999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="40"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="40"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>